--- a/data/CS1/Location1/Location1_operational_data.xlsx
+++ b/data/CS1/Location1/Location1_operational_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/HR1/Location1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/Location1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F911B5-8992-E64C-81B1-B659D081D0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9981D7BC-2883-FD40-9391-5603C71A56DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8260" yWindow="6360" windowWidth="19080" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57060" yWindow="4680" windowWidth="32660" windowHeight="19280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="23">
   <si>
     <t>Pc</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>Pc_prev</t>
+  </si>
+  <si>
+    <t>Qc_prev</t>
   </si>
 </sst>
 </file>
@@ -463,13 +469,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -482,425 +488,573 @@
       <c r="D1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" cm="1">
-        <f t="array" ref="B2">MAX(ABS('Pc, Original'!$D2:$AA2))</f>
-        <v>3.4130000000000003</v>
-      </c>
-      <c r="C2" cm="1">
-        <f t="array" ref="C2">MAX(ABS('Qc, Original'!$D2:$AA2))</f>
-        <v>1.746</v>
+      <c r="B2" s="1">
+        <v>3.6989999999999998</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3.153</v>
       </c>
       <c r="D2" s="2">
         <f>B2/SUM($B$2:$B$27)</f>
-        <v>4.1147748508047512E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>9.1438928362457105E-3</v>
+      </c>
+      <c r="G2" cm="1">
+        <f t="array" ref="G2">MAX(ABS('Pc, Original'!$D2:$AA2))</f>
+        <v>3.4130000000000003</v>
+      </c>
+      <c r="H2" cm="1">
+        <f t="array" ref="H2">MAX(ABS('Qc, Original'!$D2:$AA2))</f>
+        <v>1.746</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" cm="1">
-        <f t="array" ref="B3">MAX(ABS('Pc, Original'!$D3:$AA3))</f>
+      <c r="B3" s="1">
+        <v>25.396999999999998</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D26" si="0">B3/SUM($B$2:$B$27)</f>
+        <v>6.2781142568838141E-2</v>
+      </c>
+      <c r="G3" cm="1">
+        <f t="array" ref="G3">MAX(ABS('Pc, Original'!$D3:$AA3))</f>
         <v>28.920999999999999</v>
       </c>
-      <c r="C3" cm="1">
-        <f t="array" ref="C3">MAX(ABS('Qc, Original'!$D3:$AA3))</f>
+      <c r="H3" cm="1">
+        <f t="array" ref="H3">MAX(ABS('Qc, Original'!$D3:$AA3))</f>
         <v>4.1769999999999996</v>
       </c>
-      <c r="D3" s="2">
-        <f t="shared" ref="D3:D27" si="0">B3/SUM($B$2:$B$27)</f>
-        <v>3.4867683404665742E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" cm="1">
-        <f t="array" ref="B4">MAX(ABS('Pc, Original'!$D4:$AA4))</f>
+      <c r="B4" s="1">
+        <v>38.622</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.379</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>9.5473216848197304E-2</v>
+      </c>
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">MAX(ABS('Pc, Original'!$D4:$AA4))</f>
         <v>34.793999999999997</v>
       </c>
-      <c r="C4" cm="1">
-        <f t="array" ref="C4">MAX(ABS('Qc, Original'!$D4:$AA4))</f>
+      <c r="H4" cm="1">
+        <f t="array" ref="H4">MAX(ABS('Qc, Original'!$D4:$AA4))</f>
         <v>4.4930000000000003</v>
       </c>
-      <c r="D4" s="2">
-        <f t="shared" si="0"/>
-        <v>4.1948278980047021E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" cm="1">
-        <f t="array" ref="B5">MAX(ABS('Pc, Original'!$D5:$AA5))</f>
+      <c r="B5" s="1">
+        <v>46.624000000000002</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7.7750000000000004</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11525408477889161</v>
+      </c>
+      <c r="G5" cm="1">
+        <f t="array" ref="G5">MAX(ABS('Pc, Original'!$D5:$AA5))</f>
         <v>93.512</v>
       </c>
-      <c r="C5" cm="1">
-        <f t="array" ref="C5">MAX(ABS('Qc, Original'!$D5:$AA5))</f>
+      <c r="H5" cm="1">
+        <f t="array" ref="H5">MAX(ABS('Qc, Original'!$D5:$AA5))</f>
         <v>20.027000000000001</v>
       </c>
-      <c r="D5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.11273976731569113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" cm="1">
-        <f t="array" ref="B6">MAX(ABS('Pc, Original'!$D6:$AA6))</f>
+      <c r="B6" s="1">
+        <v>9.8160000000000007</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.853</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>2.4265058686290322E-2</v>
+      </c>
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">MAX(ABS('Pc, Original'!$D6:$AA6))</f>
         <v>11.846</v>
       </c>
-      <c r="C6" cm="1">
-        <f t="array" ref="C6">MAX(ABS('Qc, Original'!$D6:$AA6))</f>
+      <c r="H6" cm="1">
+        <f t="array" ref="H6">MAX(ABS('Qc, Original'!$D6:$AA6))</f>
         <v>2.0989999999999998</v>
       </c>
-      <c r="D6" s="2">
-        <f t="shared" si="0"/>
-        <v>1.4281752968834771E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" cm="1">
-        <f t="array" ref="B7">MAX(ABS('Pc, Original'!$D7:$AA7))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" cm="1">
-        <f t="array" ref="C7">MAX(ABS('Qc, Original'!$D7:$AA7))</f>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">MAX(ABS('Pc, Original'!$D7:$AA7))</f>
+        <v>0</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7">MAX(ABS('Qc, Original'!$D7:$AA7))</f>
         <v>99.828999999999994</v>
       </c>
-      <c r="D7" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" cm="1">
-        <f t="array" ref="B8">MAX(ABS('Pc, Original'!$D8:$AA8))</f>
+      <c r="B8" s="1">
+        <v>18.896000000000001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>8.7539999999999996</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>4.6710732369207614E-2</v>
+      </c>
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">MAX(ABS('Pc, Original'!$D8:$AA8))</f>
         <v>33.956000000000003</v>
       </c>
-      <c r="C8" cm="1">
-        <f t="array" ref="C8">MAX(ABS('Qc, Original'!$D8:$AA8))</f>
+      <c r="H8" cm="1">
+        <f t="array" ref="H8">MAX(ABS('Qc, Original'!$D8:$AA8))</f>
         <v>13.311999999999999</v>
       </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>4.0937970944601852E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" cm="1">
-        <f t="array" ref="B9">MAX(ABS('Pc, Original'!$D9:$AA9))</f>
+      <c r="B9" s="1">
+        <v>32.695</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4.319</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>8.0821729191958236E-2</v>
+      </c>
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">MAX(ABS('Pc, Original'!$D9:$AA9))</f>
         <v>46.826000000000001</v>
       </c>
-      <c r="C9" cm="1">
-        <f t="array" ref="C9">MAX(ABS('Qc, Original'!$D9:$AA9))</f>
+      <c r="H9" cm="1">
+        <f t="array" ref="H9">MAX(ABS('Qc, Original'!$D9:$AA9))</f>
         <v>16.129000000000001</v>
       </c>
-      <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>5.6454276930496115E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" cm="1">
-        <f t="array" ref="B10">MAX(ABS('Pc, Original'!$D10:$AA10))</f>
+      <c r="B10" s="1">
+        <v>18.8523</v>
+      </c>
+      <c r="C10" s="1">
+        <v>-1.46</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>4.6602706384632334E-2</v>
+      </c>
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">MAX(ABS('Pc, Original'!$D10:$AA10))</f>
         <v>306.23700000000002</v>
       </c>
-      <c r="C10" cm="1">
-        <f t="array" ref="C10">MAX(ABS('Qc, Original'!$D10:$AA10))</f>
+      <c r="H10" cm="1">
+        <f t="array" ref="H10">MAX(ABS('Qc, Original'!$D10:$AA10))</f>
         <v>37.097999999999999</v>
       </c>
-      <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>0.36920489480981378</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" cm="1">
-        <f t="array" ref="B11">MAX(ABS('Pc, Original'!$D11:$AA11))</f>
+      <c r="B11" s="1">
+        <v>4.3179999999999996</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-7.359</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0674054951854278E-2</v>
+      </c>
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">MAX(ABS('Pc, Original'!$D11:$AA11))</f>
         <v>5.9770000000000003</v>
       </c>
-      <c r="C11" cm="1">
-        <f t="array" ref="C11">MAX(ABS('Qc, Original'!$D11:$AA11))</f>
+      <c r="H11" cm="1">
+        <f t="array" ref="H11">MAX(ABS('Qc, Original'!$D11:$AA11))</f>
         <v>3.4350000000000001</v>
       </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>7.2059798661763827E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" cm="1">
-        <f t="array" ref="B12">MAX(ABS('Pc, Original'!$D12:$AA12))</f>
+      <c r="B12" s="1">
+        <v>33.231000000000002</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3.907</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>8.2146716096588607E-2</v>
+      </c>
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">MAX(ABS('Pc, Original'!$D12:$AA12))</f>
         <v>50.106999999999999</v>
       </c>
-      <c r="C12" cm="1">
-        <f t="array" ref="C12">MAX(ABS('Qc, Original'!$D12:$AA12))</f>
+      <c r="H12" cm="1">
+        <f t="array" ref="H12">MAX(ABS('Qc, Original'!$D12:$AA12))</f>
         <v>8.2629999999999999</v>
       </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
-        <v>6.0409910181445543E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" cm="1">
-        <f t="array" ref="B13">MAX(ABS('Pc, Original'!$D13:$AA13))</f>
+      <c r="B13" s="1">
+        <v>8.2249999999999996</v>
+      </c>
+      <c r="C13" s="1">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>2.0332121810792369E-2</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">MAX(ABS('Pc, Original'!$D13:$AA13))</f>
         <v>10.686999999999999</v>
       </c>
-      <c r="C13" cm="1">
-        <f t="array" ref="C13">MAX(ABS('Qc, Original'!$D13:$AA13))</f>
+      <c r="H13" cm="1">
+        <f t="array" ref="H13">MAX(ABS('Qc, Original'!$D13:$AA13))</f>
         <v>1.5919999999999999</v>
       </c>
-      <c r="D13" s="2">
-        <f t="shared" si="0"/>
-        <v>1.2884441497377781E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" cm="1">
-        <f t="array" ref="B14">MAX(ABS('Pc, Original'!$D14:$AA14))</f>
+      <c r="B14" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>-1.5269999999999999</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>3.9551847899413732E-3</v>
+      </c>
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">MAX(ABS('Pc, Original'!$D14:$AA14))</f>
         <v>1.5489999999999999</v>
       </c>
-      <c r="C14" cm="1">
-        <f t="array" ref="C14">MAX(ABS('Qc, Original'!$D14:$AA14))</f>
+      <c r="H14" cm="1">
+        <f t="array" ref="H14">MAX(ABS('Qc, Original'!$D14:$AA14))</f>
         <v>1.034</v>
       </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>1.8675025619386341E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" cm="1">
-        <f t="array" ref="B15">MAX(ABS('Pc, Original'!$D15:$AA15))</f>
+      <c r="B15" s="1">
+        <v>4.3250000000000002</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-0.51600000000000001</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0691358885310273E-2</v>
+      </c>
+      <c r="G15" cm="1">
+        <f t="array" ref="G15">MAX(ABS('Pc, Original'!$D15:$AA15))</f>
         <v>4.3029999999999999</v>
       </c>
-      <c r="C15" cm="1">
-        <f t="array" ref="C15">MAX(ABS('Qc, Original'!$D15:$AA15))</f>
+      <c r="H15" cm="1">
+        <f t="array" ref="H15">MAX(ABS('Qc, Original'!$D15:$AA15))</f>
         <v>0.93300000000000005</v>
       </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>5.1877750316474775E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" cm="1">
-        <f t="array" ref="B16">MAX(ABS('Pc, Original'!$D16:$AA16))</f>
+      <c r="B16" s="1">
+        <v>9.66</v>
+      </c>
+      <c r="C16" s="1">
+        <v>-6.3E-2</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>2.3879428169271039E-2</v>
+      </c>
+      <c r="G16" cm="1">
+        <f t="array" ref="G16">MAX(ABS('Pc, Original'!$D16:$AA16))</f>
         <v>11.805</v>
       </c>
-      <c r="C16" cm="1">
-        <f t="array" ref="C16">MAX(ABS('Qc, Original'!$D16:$AA16))</f>
+      <c r="H16" cm="1">
+        <f t="array" ref="H16">MAX(ABS('Qc, Original'!$D16:$AA16))</f>
         <v>1.635</v>
       </c>
-      <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>1.4232322623425163E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" cm="1">
-        <f t="array" ref="B17">MAX(ABS('Pc, Original'!$D17:$AA17))</f>
+      <c r="B17" s="1">
+        <v>30.047999999999998</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3.831</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>7.4278370355098974E-2</v>
+      </c>
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">MAX(ABS('Pc, Original'!$D17:$AA17))</f>
         <v>31.018999999999998</v>
       </c>
-      <c r="C17" cm="1">
-        <f t="array" ref="C17">MAX(ABS('Qc, Original'!$D17:$AA17))</f>
+      <c r="H17" cm="1">
+        <f t="array" ref="H17">MAX(ABS('Qc, Original'!$D17:$AA17))</f>
         <v>5.13</v>
       </c>
-      <c r="D17" s="2">
-        <f t="shared" si="0"/>
-        <v>3.7397070347820846E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" cm="1">
-        <f t="array" ref="B18">MAX(ABS('Pc, Original'!$D18:$AA18))</f>
+      <c r="B18" s="1">
+        <v>14.775</v>
+      </c>
+      <c r="C18" s="1">
+        <v>-0.35799999999999998</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>3.6523659544614867E-2</v>
+      </c>
+      <c r="G18" cm="1">
+        <f t="array" ref="G18">MAX(ABS('Pc, Original'!$D18:$AA18))</f>
         <v>15.894</v>
       </c>
-      <c r="C18" cm="1">
-        <f t="array" ref="C18">MAX(ABS('Qc, Original'!$D18:$AA18))</f>
+      <c r="H18" cm="1">
+        <f t="array" ref="H18">MAX(ABS('Qc, Original'!$D18:$AA18))</f>
         <v>1.9330000000000001</v>
       </c>
-      <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>1.9162095364398096E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" cm="1">
-        <f t="array" ref="B19">MAX(ABS('Pc, Original'!$D19:$AA19))</f>
+      <c r="B19" s="1">
+        <v>15.904999999999999</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.7729999999999999</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>3.9317008802510954E-2</v>
+      </c>
+      <c r="G19" cm="1">
+        <f t="array" ref="G19">MAX(ABS('Pc, Original'!$D19:$AA19))</f>
         <v>30.071000000000002</v>
       </c>
-      <c r="C19" cm="1">
-        <f t="array" ref="C19">MAX(ABS('Qc, Original'!$D19:$AA19))</f>
+      <c r="H19" cm="1">
+        <f t="array" ref="H19">MAX(ABS('Qc, Original'!$D19:$AA19))</f>
         <v>4.25</v>
       </c>
-      <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>3.6254144312496239E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" cm="1">
-        <f t="array" ref="B20">MAX(ABS('Pc, Original'!$D20:$AA20))</f>
+      <c r="B20" s="1">
+        <v>-0.80600000000000005</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.1030000000000002</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.9924243379329668E-3</v>
+      </c>
+      <c r="G20" cm="1">
+        <f t="array" ref="G20">MAX(ABS('Pc, Original'!$D20:$AA20))</f>
         <v>1.86</v>
       </c>
-      <c r="C20" cm="1">
-        <f t="array" ref="C20">MAX(ABS('Qc, Original'!$D20:$AA20))</f>
+      <c r="H20" cm="1">
+        <f t="array" ref="H20">MAX(ABS('Qc, Original'!$D20:$AA20))</f>
         <v>2.347</v>
       </c>
-      <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>2.2424498161432277E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" cm="1">
-        <f t="array" ref="B21">MAX(ABS('Pc, Original'!$D21:$AA21))</f>
+      <c r="B21" s="1">
+        <v>21.279</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1.8520000000000001</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>5.2601485715726544E-2</v>
+      </c>
+      <c r="G21" cm="1">
+        <f t="array" ref="G21">MAX(ABS('Pc, Original'!$D21:$AA21))</f>
         <v>22.466000000000001</v>
       </c>
-      <c r="C21" cm="1">
-        <f t="array" ref="C21">MAX(ABS('Qc, Original'!$D21:$AA21))</f>
+      <c r="H21" cm="1">
+        <f t="array" ref="H21">MAX(ABS('Qc, Original'!$D21:$AA21))</f>
         <v>3.052</v>
       </c>
-      <c r="D21" s="2">
-        <f t="shared" si="0"/>
-        <v>2.708541804810417E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" cm="1">
-        <f t="array" ref="B22">MAX(ABS('Pc, Original'!$D22:$AA22))</f>
+      <c r="B22" s="1">
+        <v>7.1059999999999999</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1.0580000000000001</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7565964448327122E-2</v>
+      </c>
+      <c r="G22" cm="1">
+        <f t="array" ref="G22">MAX(ABS('Pc, Original'!$D22:$AA22))</f>
         <v>5.8520000000000003</v>
       </c>
-      <c r="C22" cm="1">
-        <f t="array" ref="C22">MAX(ABS('Qc, Original'!$D22:$AA22))</f>
+      <c r="H22" cm="1">
+        <f t="array" ref="H22">MAX(ABS('Qc, Original'!$D22:$AA22))</f>
         <v>0.75800000000000001</v>
       </c>
-      <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>7.0552775935861121E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" cm="1">
-        <f t="array" ref="B23">MAX(ABS('Pc, Original'!$D23:$AA23))</f>
+      <c r="B23" s="1">
+        <v>5.7069999999999999</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.4860000000000002</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>1.4107649747622134E-2</v>
+      </c>
+      <c r="G23" cm="1">
+        <f t="array" ref="G23">MAX(ABS('Pc, Original'!$D23:$AA23))</f>
         <v>6.9669999999999996</v>
       </c>
-      <c r="C23" cm="1">
-        <f t="array" ref="C23">MAX(ABS('Qc, Original'!$D23:$AA23))</f>
+      <c r="H23" cm="1">
+        <f t="array" ref="H23">MAX(ABS('Qc, Original'!$D23:$AA23))</f>
         <v>2.2690000000000001</v>
       </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>8.3995418650913267E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" cm="1">
-        <f t="array" ref="B24">MAX(ABS('Pc, Original'!$D24:$AA24))</f>
+      <c r="B24" s="1">
+        <v>11.648999999999999</v>
+      </c>
+      <c r="C24" s="1">
+        <v>8.0169999999999995</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>2.8796217261266903E-2</v>
+      </c>
+      <c r="G24" cm="1">
+        <f t="array" ref="G24">MAX(ABS('Pc, Original'!$D24:$AA24))</f>
         <v>37.238</v>
       </c>
-      <c r="C24" cm="1">
-        <f t="array" ref="C24">MAX(ABS('Qc, Original'!$D24:$AA24))</f>
+      <c r="H24" cm="1">
+        <f t="array" ref="H24">MAX(ABS('Qc, Original'!$D24:$AA24))</f>
         <v>9.657</v>
       </c>
-      <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>4.4894809813731992E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" cm="1">
-        <f t="array" ref="B25">MAX(ABS('Pc, Original'!$D25:$AA25))</f>
+      <c r="B25" s="1">
+        <v>42.908999999999999</v>
+      </c>
+      <c r="C25" s="1">
+        <v>12.673</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.10607064009474647</v>
+      </c>
+      <c r="G25" cm="1">
+        <f t="array" ref="G25">MAX(ABS('Pc, Original'!$D25:$AA25))</f>
         <v>34.150000000000006</v>
       </c>
-      <c r="C25" cm="1">
-        <f t="array" ref="C25">MAX(ABS('Qc, Original'!$D25:$AA25))</f>
+      <c r="H25" cm="1">
+        <f t="array" ref="H25">MAX(ABS('Qc, Original'!$D25:$AA25))</f>
         <v>22.333000000000002</v>
       </c>
-      <c r="D25" s="2">
-        <f t="shared" si="0"/>
-        <v>4.1171860871661956E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" cm="1">
-        <f t="array" ref="B26">MAX(ABS('Pc, Original'!$D26:$AA26))</f>
-        <v>0</v>
-      </c>
-      <c r="C26" cm="1">
-        <f t="array" ref="C26">MAX(ABS('Qc, Original'!$D26:$AA26))</f>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
         <v>0</v>
       </c>
       <c r="D26" s="2">
@@ -908,44 +1062,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" cm="1">
-        <f t="array" ref="B27">MAX(ABS('Pc, Original'!$D27:$AA27))</f>
-        <v>0</v>
-      </c>
-      <c r="C27" cm="1">
-        <f t="array" ref="C27">MAX(ABS('Qc, Original'!$D27:$AA27))</f>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+        <f>B27/SUM($B$2:$B$27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
